--- a/public_administration_forms/015_urban_planning_community_needs_survey--public_administration_forms.xlsx
+++ b/public_administration_forms/015_urban_planning_community_needs_survey--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -758,8 +758,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,12 +787,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'housing'}</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Housing'}</t>
+          <t>Housing</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'public_safety'}</t>
+          <t>public_safety</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Public Safety'}</t>
+          <t>Public Safety</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'public_spaces'}</t>
+          <t>public_spaces</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Public Spaces'}</t>
+          <t>Public Spaces</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'public_parks'}</t>
+          <t>public_parks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Public Parks'}</t>
+          <t>Public Parks</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'public_schools'}</t>
+          <t>public_schools</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Public Schools'}</t>
+          <t>Public Schools</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'public_libraries'}</t>
+          <t>public_libraries</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Public Libraries'}</t>
+          <t>Public Libraries</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'public_restrooms'}</t>
+          <t>public_restrooms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Public Restrooms'}</t>
+          <t>Public Restrooms</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'public_sports_facilities'}</t>
+          <t>public_sports_facilities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Public Sports Facilities'}</t>
+          <t>Public Sports Facilities</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'affordable_housing'}</t>
+          <t>affordable_housing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Affordable Housing'}</t>
+          <t>Affordable Housing</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'community_engagement'}</t>
+          <t>community_engagement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Community Engagement'}</t>
+          <t>Community Engagement</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'local_businesses'}</t>
+          <t>local_businesses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Local Businesses'}</t>
+          <t>Local Businesses</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'public_transportation'}</t>
+          <t>public_transportation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Public Transportation'}</t>
+          <t>Public Transportation</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'safety_and_security'}</t>
+          <t>safety_and_security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Safety and Security'}</t>
+          <t>Safety and Security</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
